--- a/VerveStacks_POL_grids_kan50/SuppXLS/Scen_TSParameters_ts_40.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/Scen_TSParameters_ts_40.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1E5F8C30-75B0-4055-AE15-3A68CB454071}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C4E369C-0E30-4A4D-8B2D-BFC1B744CFDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ev_charging_uc" sheetId="6" r:id="rId1"/>
@@ -19,9 +19,6 @@
     <sheet name="firmness" sheetId="9" r:id="rId4"/>
     <sheet name="load_demand_peak_hydro" sheetId="10" r:id="rId5"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId6"/>
-  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -40,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7140" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7141" uniqueCount="222">
   <si>
     <t>share of charging at night</t>
   </si>
@@ -678,13 +675,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S04aH02,S02aH06,S03aH05,S03aH08,S04aH07,S01aH04,S01aH07,S02aH07,S03aH04,S04aH03,S03aH02,S03aH03,S04aH06,S01aH03,S02aH04,S02aH05,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S02aH02,S01aH06,S02aH03,S01aH02,S04aH04,S04aH05,S04aH08</t>
+    <t>S02aH06,S03aH05,S03aH08,S04aH07,S04aH03,S03aH02,S03aH03,S02aH02,S04aH06,S04aH02,S02aH04,S02aH05,S01aH02,S04aH04,S01aH03,S01aH04,S01aH07,S02aH07,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S04aH05,S04aH08,S03aH04,S01aH06,S02aH03</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S01aH10,S03aH02,S03aH09,S01aH09,S02aH09,S04aH09,S02aH01,S02aH10,S04aH02,S02aH02,S04aH10,S04aH08,S03aH08,S03aH10,S01aH02,S03aH01,S01aH01,S04aH01,S01aH08,S02aH08</t>
+    <t>S03aH09,S02aH01,S02aH10,S04aH02,S02aH02,S04aH10,S03aH01,S01aH10,S03aH02,S03aH08,S03aH10,S01aH08,S02aH08,S01aH09,S01aH02,S02aH09,S04aH09,S01aH01,S04aH01,S04aH08</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -845,19 +842,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Veda"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1181,9 +1165,8 @@
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="10" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A10" t="str">
-        <f>IFERROR([1]Veda!D5,"ts_40")</f>
-        <v>ts_40</v>
+      <c r="A10" t="s">
+        <v>53</v>
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5" t="s">
@@ -1279,7 +1262,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S01aH10,S03aH02,S03aH09,S01aH09,S02aH09,S04aH09,S02aH01,S02aH10,S04aH02,S02aH02,S04aH10,S04aH08,S03aH08,S03aH10,S01aH02,S03aH01,S01aH01,S04aH01,S01aH08,S02aH08</v>
+        <v>S03aH09,S02aH01,S02aH10,S04aH02,S02aH02,S04aH10,S03aH01,S01aH10,S03aH02,S03aH08,S03aH10,S01aH08,S02aH08,S01aH09,S01aH02,S02aH09,S04aH09,S01aH01,S04aH01,S04aH08</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1311,7 +1294,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S04aH02,S02aH06,S03aH05,S03aH08,S04aH07,S01aH04,S01aH07,S02aH07,S03aH04,S04aH03,S03aH02,S03aH03,S04aH06,S01aH03,S02aH04,S02aH05,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S02aH02,S01aH06,S02aH03,S01aH02,S04aH04,S04aH05,S04aH08</v>
+        <v>S02aH06,S03aH05,S03aH08,S04aH07,S04aH03,S03aH02,S03aH03,S02aH02,S04aH06,S04aH02,S02aH04,S02aH05,S01aH02,S04aH04,S01aH03,S01aH04,S01aH07,S02aH07,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S04aH05,S04aH08,S03aH04,S01aH06,S02aH03</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1407,7 +1390,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C57A9FF-0603-4247-83B8-764CB67ADF82}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1941243E-8524-4540-9B67-6550DB41EC7E}">
   <dimension ref="A9:G20"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1438,10 +1421,6 @@
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A11" t="str">
-        <f>IFERROR(IF([1]Veda!D5=A10,"ok","x"),"")</f>
-        <v/>
-      </c>
       <c r="C11" t="s">
         <v>37</v>
       </c>
@@ -1545,7 +1524,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DA08A28-211A-426A-8901-46AB4283C80A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FD229C1-8FFC-4E42-9C12-4F3286FB992C}">
   <dimension ref="B9:O810"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -27207,7 +27186,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3B3075B-B35D-412D-94ED-ECEB3B237F71}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E95C2D9B-1156-4CC7-A53E-EF926FA0C1D1}">
   <dimension ref="B9:FT60"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -41660,7 +41639,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7264771D-C952-4A49-9FB4-CF12D07B6C62}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C392BC-36B7-42C8-A025-738DC82D9F4B}">
   <dimension ref="A9:S126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -41730,10 +41709,6 @@
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.45">
-      <c r="A11" t="str">
-        <f>IFERROR(IF([1]Veda!D5=A10,"ok","x"),"")</f>
-        <v/>
-      </c>
       <c r="C11">
         <v>5.1369863013698627E-2</v>
       </c>
@@ -41891,7 +41866,7 @@
         <v>45</v>
       </c>
       <c r="R14">
-        <v>0.19110000000000002</v>
+        <v>0.19109999999999996</v>
       </c>
       <c r="S14" t="s">
         <v>221</v>
@@ -41932,7 +41907,7 @@
         <v>37</v>
       </c>
       <c r="R15">
-        <v>0.20653333333333335</v>
+        <v>0.20653333333333332</v>
       </c>
       <c r="S15" t="s">
         <v>221</v>
@@ -42137,7 +42112,7 @@
         <v>41</v>
       </c>
       <c r="R20">
-        <v>0.23150000000000001</v>
+        <v>0.23149999999999996</v>
       </c>
       <c r="S20" t="s">
         <v>221</v>
@@ -42342,7 +42317,7 @@
         <v>43</v>
       </c>
       <c r="R25">
-        <v>0.24466666666666667</v>
+        <v>0.2446666666666667</v>
       </c>
       <c r="S25" t="s">
         <v>221</v>
@@ -42793,7 +42768,7 @@
         <v>41</v>
       </c>
       <c r="R36">
-        <v>0.32773333333333338</v>
+        <v>0.32773333333333332</v>
       </c>
       <c r="S36" t="s">
         <v>221</v>
@@ -43121,7 +43096,7 @@
         <v>41</v>
       </c>
       <c r="R44">
-        <v>0.34233333333333338</v>
+        <v>0.34233333333333332</v>
       </c>
       <c r="S44" t="s">
         <v>221</v>
@@ -43244,7 +43219,7 @@
         <v>37</v>
       </c>
       <c r="R47">
-        <v>0.30260000000000004</v>
+        <v>0.30259999999999998</v>
       </c>
       <c r="S47" t="s">
         <v>221</v>
@@ -43367,7 +43342,7 @@
         <v>45</v>
       </c>
       <c r="R50">
-        <v>0.24779999999999999</v>
+        <v>0.24780000000000002</v>
       </c>
       <c r="S50" t="s">
         <v>221</v>
@@ -43447,7 +43422,7 @@
         <v>45</v>
       </c>
       <c r="R54">
-        <v>0.22766666666666668</v>
+        <v>0.22766666666666666</v>
       </c>
       <c r="S54" t="s">
         <v>221</v>
@@ -43487,7 +43462,7 @@
         <v>41</v>
       </c>
       <c r="R56">
-        <v>0.35000000000000003</v>
+        <v>0.34999999999999992</v>
       </c>
       <c r="S56" t="s">
         <v>221</v>
@@ -43507,7 +43482,7 @@
         <v>43</v>
       </c>
       <c r="R57">
-        <v>0.18733333333333332</v>
+        <v>0.18733333333333335</v>
       </c>
       <c r="S57" t="s">
         <v>221</v>
@@ -43547,7 +43522,7 @@
         <v>37</v>
       </c>
       <c r="R59">
-        <v>0.29859999999999998</v>
+        <v>0.29860000000000003</v>
       </c>
       <c r="S59" t="s">
         <v>221</v>
@@ -43587,7 +43562,7 @@
         <v>43</v>
       </c>
       <c r="R61">
-        <v>0.20516666666666669</v>
+        <v>0.20516666666666664</v>
       </c>
       <c r="S61" t="s">
         <v>221</v>
@@ -43647,7 +43622,7 @@
         <v>41</v>
       </c>
       <c r="R64">
-        <v>0.32976666666666665</v>
+        <v>0.3297666666666666</v>
       </c>
       <c r="S64" t="s">
         <v>221</v>
@@ -43667,7 +43642,7 @@
         <v>43</v>
       </c>
       <c r="R65">
-        <v>0.20076666666666668</v>
+        <v>0.20076666666666665</v>
       </c>
       <c r="S65" t="s">
         <v>221</v>
@@ -43707,7 +43682,7 @@
         <v>37</v>
       </c>
       <c r="R67">
-        <v>0.37279999999999996</v>
+        <v>0.37280000000000002</v>
       </c>
       <c r="S67" t="s">
         <v>221</v>
@@ -43727,7 +43702,7 @@
         <v>41</v>
       </c>
       <c r="R68">
-        <v>0.38203333333333328</v>
+        <v>0.38203333333333339</v>
       </c>
       <c r="S68" t="s">
         <v>221</v>
@@ -43827,7 +43802,7 @@
         <v>43</v>
       </c>
       <c r="R73">
-        <v>0.19603333333333336</v>
+        <v>0.19603333333333331</v>
       </c>
       <c r="S73" t="s">
         <v>221</v>
@@ -43907,7 +43882,7 @@
         <v>43</v>
       </c>
       <c r="R77">
-        <v>0.21279999999999999</v>
+        <v>0.21280000000000002</v>
       </c>
       <c r="S77" t="s">
         <v>221</v>
@@ -43947,7 +43922,7 @@
         <v>37</v>
       </c>
       <c r="R79">
-        <v>0.32426666666666665</v>
+        <v>0.3242666666666667</v>
       </c>
       <c r="S79" t="s">
         <v>221</v>
@@ -44027,7 +44002,7 @@
         <v>37</v>
       </c>
       <c r="R83">
-        <v>0.30743333333333328</v>
+        <v>0.30743333333333334</v>
       </c>
       <c r="S83" t="s">
         <v>221</v>
@@ -44047,7 +44022,7 @@
         <v>41</v>
       </c>
       <c r="R84">
-        <v>0.3323666666666667</v>
+        <v>0.33236666666666664</v>
       </c>
       <c r="S84" t="s">
         <v>221</v>
@@ -44181,7 +44156,7 @@
         <v>37</v>
       </c>
       <c r="R91">
-        <v>0.31433333333333335</v>
+        <v>0.3143333333333333</v>
       </c>
       <c r="S91" t="s">
         <v>221</v>
@@ -44223,7 +44198,7 @@
         <v>45</v>
       </c>
       <c r="R94">
-        <v>0.21929999999999997</v>
+        <v>0.21930000000000002</v>
       </c>
       <c r="S94" t="s">
         <v>221</v>
@@ -44363,7 +44338,7 @@
         <v>41</v>
       </c>
       <c r="R104">
-        <v>0.32653333333333329</v>
+        <v>0.32653333333333334</v>
       </c>
       <c r="S104" t="s">
         <v>221</v>
@@ -44461,7 +44436,7 @@
         <v>37</v>
       </c>
       <c r="R111">
-        <v>0.31430000000000002</v>
+        <v>0.31429999999999997</v>
       </c>
       <c r="S111" t="s">
         <v>221</v>
@@ -44531,7 +44506,7 @@
         <v>41</v>
       </c>
       <c r="R116">
-        <v>0.32293333333333335</v>
+        <v>0.32293333333333329</v>
       </c>
       <c r="S116" t="s">
         <v>221</v>
@@ -44573,7 +44548,7 @@
         <v>37</v>
       </c>
       <c r="R119">
-        <v>0.31936666666666669</v>
+        <v>0.31936666666666663</v>
       </c>
       <c r="S119" t="s">
         <v>221</v>
@@ -44615,7 +44590,7 @@
         <v>45</v>
       </c>
       <c r="R122">
-        <v>0.23019999999999999</v>
+        <v>0.23020000000000004</v>
       </c>
       <c r="S122" t="s">
         <v>221</v>
@@ -44643,7 +44618,7 @@
         <v>41</v>
       </c>
       <c r="R124">
-        <v>0.35573333333333329</v>
+        <v>0.3557333333333334</v>
       </c>
       <c r="S124" t="s">
         <v>221</v>
@@ -44657,7 +44632,7 @@
         <v>43</v>
       </c>
       <c r="R125">
-        <v>0.17353333333333334</v>
+        <v>0.17353333333333332</v>
       </c>
       <c r="S125" t="s">
         <v>221</v>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/Scen_TSParameters_ts_40.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/Scen_TSParameters_ts_40.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C4E369C-0E30-4A4D-8B2D-BFC1B744CFDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60BA4C6F-08EE-44AE-97BD-B682934C46FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -675,13 +675,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S02aH06,S03aH05,S03aH08,S04aH07,S04aH03,S03aH02,S03aH03,S02aH02,S04aH06,S04aH02,S02aH04,S02aH05,S01aH02,S04aH04,S01aH03,S01aH04,S01aH07,S02aH07,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S04aH05,S04aH08,S03aH04,S01aH06,S02aH03</t>
+    <t>S01aH06,S02aH03,S02aH06,S03aH05,S03aH08,S04aH07,S02aH04,S02aH05,S04aH03,S03aH03,S04aH06,S03aH04,S01aH03,S04aH02,S04aH05,S04aH08,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S01aH02,S04aH04,S01aH04,S01aH07,S02aH07,S02aH02,S03aH02</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S03aH09,S02aH01,S02aH10,S04aH02,S02aH02,S04aH10,S03aH01,S01aH10,S03aH02,S03aH08,S03aH10,S01aH08,S02aH08,S01aH09,S01aH02,S02aH09,S04aH09,S01aH01,S04aH01,S04aH08</t>
+    <t>S01aH01,S04aH01,S03aH09,S03aH08,S03aH10,S02aH01,S02aH10,S04aH08,S02aH02,S04aH10,S02aH09,S04aH09,S01aH10,S03aH02,S01aH02,S01aH08,S02aH08,S01aH09,S03aH01,S04aH02</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1262,7 +1262,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S03aH09,S02aH01,S02aH10,S04aH02,S02aH02,S04aH10,S03aH01,S01aH10,S03aH02,S03aH08,S03aH10,S01aH08,S02aH08,S01aH09,S01aH02,S02aH09,S04aH09,S01aH01,S04aH01,S04aH08</v>
+        <v>S01aH01,S04aH01,S03aH09,S03aH08,S03aH10,S02aH01,S02aH10,S04aH08,S02aH02,S04aH10,S02aH09,S04aH09,S01aH10,S03aH02,S01aH02,S01aH08,S02aH08,S01aH09,S03aH01,S04aH02</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S02aH06,S03aH05,S03aH08,S04aH07,S04aH03,S03aH02,S03aH03,S02aH02,S04aH06,S04aH02,S02aH04,S02aH05,S01aH02,S04aH04,S01aH03,S01aH04,S01aH07,S02aH07,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S04aH05,S04aH08,S03aH04,S01aH06,S02aH03</v>
+        <v>S01aH06,S02aH03,S02aH06,S03aH05,S03aH08,S04aH07,S02aH04,S02aH05,S04aH03,S03aH03,S04aH06,S03aH04,S01aH03,S04aH02,S04aH05,S04aH08,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S01aH02,S04aH04,S01aH04,S01aH07,S02aH07,S02aH02,S03aH02</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1390,7 +1390,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1941243E-8524-4540-9B67-6550DB41EC7E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F265FB4-59B8-4841-8247-FEB4E97D4CB6}">
   <dimension ref="A9:G20"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1524,7 +1524,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FD229C1-8FFC-4E42-9C12-4F3286FB992C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D6E0DF6-1D76-465E-9060-2F61ED420041}">
   <dimension ref="B9:O810"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -27186,7 +27186,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E95C2D9B-1156-4CC7-A53E-EF926FA0C1D1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94C072C6-62D6-4B31-B384-538AFDF227D3}">
   <dimension ref="B9:FT60"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -41639,7 +41639,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C392BC-36B7-42C8-A025-738DC82D9F4B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D17BB82-0900-441D-A58F-5D170EB7225B}">
   <dimension ref="A9:S126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -41907,7 +41907,7 @@
         <v>37</v>
       </c>
       <c r="R15">
-        <v>0.20653333333333332</v>
+        <v>0.20653333333333335</v>
       </c>
       <c r="S15" t="s">
         <v>221</v>
@@ -42071,7 +42071,7 @@
         <v>37</v>
       </c>
       <c r="R19">
-        <v>0.23840000000000003</v>
+        <v>0.23839999999999997</v>
       </c>
       <c r="S19" t="s">
         <v>221</v>
@@ -42112,7 +42112,7 @@
         <v>41</v>
       </c>
       <c r="R20">
-        <v>0.23149999999999996</v>
+        <v>0.23150000000000001</v>
       </c>
       <c r="S20" t="s">
         <v>221</v>
@@ -42768,7 +42768,7 @@
         <v>41</v>
       </c>
       <c r="R36">
-        <v>0.32773333333333332</v>
+        <v>0.32773333333333338</v>
       </c>
       <c r="S36" t="s">
         <v>221</v>
@@ -43096,7 +43096,7 @@
         <v>41</v>
       </c>
       <c r="R44">
-        <v>0.34233333333333332</v>
+        <v>0.34233333333333338</v>
       </c>
       <c r="S44" t="s">
         <v>221</v>
@@ -43362,7 +43362,7 @@
         <v>37</v>
       </c>
       <c r="R51">
-        <v>0.31676666666666664</v>
+        <v>0.3167666666666667</v>
       </c>
       <c r="S51" t="s">
         <v>221</v>
@@ -43462,7 +43462,7 @@
         <v>41</v>
       </c>
       <c r="R56">
-        <v>0.34999999999999992</v>
+        <v>0.35000000000000003</v>
       </c>
       <c r="S56" t="s">
         <v>221</v>
@@ -43622,7 +43622,7 @@
         <v>41</v>
       </c>
       <c r="R64">
-        <v>0.3297666666666666</v>
+        <v>0.32976666666666665</v>
       </c>
       <c r="S64" t="s">
         <v>221</v>
@@ -43702,7 +43702,7 @@
         <v>41</v>
       </c>
       <c r="R68">
-        <v>0.38203333333333339</v>
+        <v>0.38203333333333328</v>
       </c>
       <c r="S68" t="s">
         <v>221</v>
@@ -43922,7 +43922,7 @@
         <v>37</v>
       </c>
       <c r="R79">
-        <v>0.3242666666666667</v>
+        <v>0.32426666666666665</v>
       </c>
       <c r="S79" t="s">
         <v>221</v>
@@ -44002,7 +44002,7 @@
         <v>37</v>
       </c>
       <c r="R83">
-        <v>0.30743333333333334</v>
+        <v>0.30743333333333328</v>
       </c>
       <c r="S83" t="s">
         <v>221</v>
@@ -44022,7 +44022,7 @@
         <v>41</v>
       </c>
       <c r="R84">
-        <v>0.33236666666666664</v>
+        <v>0.3323666666666667</v>
       </c>
       <c r="S84" t="s">
         <v>221</v>
@@ -44156,7 +44156,7 @@
         <v>37</v>
       </c>
       <c r="R91">
-        <v>0.3143333333333333</v>
+        <v>0.31433333333333335</v>
       </c>
       <c r="S91" t="s">
         <v>221</v>
@@ -44324,7 +44324,7 @@
         <v>37</v>
       </c>
       <c r="R103">
-        <v>0.28610000000000002</v>
+        <v>0.28609999999999997</v>
       </c>
       <c r="S103" t="s">
         <v>221</v>
@@ -44338,7 +44338,7 @@
         <v>41</v>
       </c>
       <c r="R104">
-        <v>0.32653333333333334</v>
+        <v>0.32653333333333329</v>
       </c>
       <c r="S104" t="s">
         <v>221</v>
@@ -44380,7 +44380,7 @@
         <v>37</v>
       </c>
       <c r="R107">
-        <v>0.32646666666666663</v>
+        <v>0.32646666666666668</v>
       </c>
       <c r="S107" t="s">
         <v>221</v>
@@ -44436,7 +44436,7 @@
         <v>37</v>
       </c>
       <c r="R111">
-        <v>0.31429999999999997</v>
+        <v>0.31430000000000002</v>
       </c>
       <c r="S111" t="s">
         <v>221</v>
@@ -44506,7 +44506,7 @@
         <v>41</v>
       </c>
       <c r="R116">
-        <v>0.32293333333333329</v>
+        <v>0.32293333333333335</v>
       </c>
       <c r="S116" t="s">
         <v>221</v>
@@ -44604,7 +44604,7 @@
         <v>37</v>
       </c>
       <c r="R123">
-        <v>0.30760000000000004</v>
+        <v>0.30759999999999998</v>
       </c>
       <c r="S123" t="s">
         <v>221</v>
@@ -44618,7 +44618,7 @@
         <v>41</v>
       </c>
       <c r="R124">
-        <v>0.3557333333333334</v>
+        <v>0.35573333333333329</v>
       </c>
       <c r="S124" t="s">
         <v>221</v>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/Scen_TSParameters_ts_40.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/Scen_TSParameters_ts_40.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{514ADFA9-D46A-4D69-B466-9CF7072EF3F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6080AEE-42D1-4CB5-9D42-0211C75C81EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -675,13 +675,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S01aH06,S02aH03,S02aH04,S02aH05,S03aH03,S01aH04,S01aH07,S02aH07,S04aH06,S02aH06,S03aH05,S03aH08,S04aH07,S03aH04,S04aH03,S03aH02,S01aH03,S04aH02,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S04aH05,S04aH08,S01aH02,S04aH04,S02aH02</t>
+    <t>S03aH04,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S03aH03,S03aH02,S04aH05,S04aH08,S02aH06,S03aH05,S03aH08,S04aH07,S04aH02,S02aH02,S01aH06,S02aH03,S04aH03,S01aH02,S04aH04,S01aH03,S01aH04,S01aH07,S02aH07,S02aH04,S02aH05,S04aH06</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S01aH01,S04aH01,S03aH08,S03aH10,S02aH02,S04aH10,S01aH09,S03aH09,S02aH09,S04aH09,S02aH01,S02aH10,S04aH02,S01aH10,S03aH02,S01aH02,S04aH08,S01aH08,S02aH08,S03aH01</t>
+    <t>S02aH09,S04aH09,S01aH02,S02aH02,S04aH10,S04aH02,S03aH09,S01aH10,S03aH02,S03aH01,S01aH01,S04aH01,S02aH01,S02aH10,S01aH08,S02aH08,S04aH08,S01aH09,S03aH08,S03aH10</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1262,7 +1262,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S01aH01,S04aH01,S03aH08,S03aH10,S02aH02,S04aH10,S01aH09,S03aH09,S02aH09,S04aH09,S02aH01,S02aH10,S04aH02,S01aH10,S03aH02,S01aH02,S04aH08,S01aH08,S02aH08,S03aH01</v>
+        <v>S02aH09,S04aH09,S01aH02,S02aH02,S04aH10,S04aH02,S03aH09,S01aH10,S03aH02,S03aH01,S01aH01,S04aH01,S02aH01,S02aH10,S01aH08,S02aH08,S04aH08,S01aH09,S03aH08,S03aH10</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S01aH06,S02aH03,S02aH04,S02aH05,S03aH03,S01aH04,S01aH07,S02aH07,S04aH06,S02aH06,S03aH05,S03aH08,S04aH07,S03aH04,S04aH03,S03aH02,S01aH03,S04aH02,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S04aH05,S04aH08,S01aH02,S04aH04,S02aH02</v>
+        <v>S03aH04,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S03aH03,S03aH02,S04aH05,S04aH08,S02aH06,S03aH05,S03aH08,S04aH07,S04aH02,S02aH02,S01aH06,S02aH03,S04aH03,S01aH02,S04aH04,S01aH03,S01aH04,S01aH07,S02aH07,S02aH04,S02aH05,S04aH06</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1390,7 +1390,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{513AFFBB-50C6-4F72-A5B3-A35CEA59B2E8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87774CA2-18C3-488E-BC4F-99A0479CCE3A}">
   <dimension ref="A9:G20"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1524,7 +1524,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C308FA4-8481-4790-ADA8-72FFF2C629A9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDE40561-5986-423A-9EFF-9F999DF099C5}">
   <dimension ref="B9:O810"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -27186,7 +27186,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4F8E48C-18C8-455E-A38D-FCA1750E39BA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CCA883F-9647-413F-89A9-6D3A6ADF5DE9}">
   <dimension ref="B9:FT60"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -41639,7 +41639,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{101A8AC0-FA54-4A0C-8B49-4AC4852AFAAD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E344CD3B-12D2-4F9F-AF2E-B4DFD3BDAE1B}">
   <dimension ref="A9:S126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -41784,7 +41784,7 @@
         <v>41</v>
       </c>
       <c r="R12">
-        <v>0.17526666666666668</v>
+        <v>0.17526666666666665</v>
       </c>
       <c r="S12" t="s">
         <v>221</v>
@@ -43382,7 +43382,7 @@
         <v>41</v>
       </c>
       <c r="R52">
-        <v>0.3227666666666667</v>
+        <v>0.32276666666666665</v>
       </c>
       <c r="S52" t="s">
         <v>221</v>
@@ -43622,7 +43622,7 @@
         <v>41</v>
       </c>
       <c r="R64">
-        <v>0.32976666666666665</v>
+        <v>0.3297666666666666</v>
       </c>
       <c r="S64" t="s">
         <v>221</v>
@@ -44170,7 +44170,7 @@
         <v>41</v>
       </c>
       <c r="R92">
-        <v>0.31546666666666673</v>
+        <v>0.31546666666666667</v>
       </c>
       <c r="S92" t="s">
         <v>221</v>
@@ -44394,7 +44394,7 @@
         <v>41</v>
       </c>
       <c r="R108">
-        <v>0.32569999999999993</v>
+        <v>0.32569999999999999</v>
       </c>
       <c r="S108" t="s">
         <v>221</v>
@@ -44618,7 +44618,7 @@
         <v>41</v>
       </c>
       <c r="R124">
-        <v>0.35573333333333329</v>
+        <v>0.3557333333333334</v>
       </c>
       <c r="S124" t="s">
         <v>221</v>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/Scen_TSParameters_ts_40.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/Scen_TSParameters_ts_40.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6080AEE-42D1-4CB5-9D42-0211C75C81EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1E9413C-5C0B-46B9-9222-A5C61258B555}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -675,13 +675,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S03aH04,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S03aH03,S03aH02,S04aH05,S04aH08,S02aH06,S03aH05,S03aH08,S04aH07,S04aH02,S02aH02,S01aH06,S02aH03,S04aH03,S01aH02,S04aH04,S01aH03,S01aH04,S01aH07,S02aH07,S02aH04,S02aH05,S04aH06</t>
+    <t>S02aH06,S03aH05,S03aH08,S04aH07,S03aH04,S01aH04,S01aH07,S02aH07,S02aH04,S02aH05,S04aH03,S03aH03,S04aH02,S03aH02,S01aH02,S04aH04,S02aH02,S01aH03,S01aH06,S02aH03,S04aH06,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S04aH05,S04aH08</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S02aH09,S04aH09,S01aH02,S02aH02,S04aH10,S04aH02,S03aH09,S01aH10,S03aH02,S03aH01,S01aH01,S04aH01,S02aH01,S02aH10,S01aH08,S02aH08,S04aH08,S01aH09,S03aH08,S03aH10</t>
+    <t>S04aH08,S03aH09,S02aH09,S04aH09,S01aH09,S03aH08,S03aH10,S02aH01,S02aH10,S02aH02,S04aH10,S01aH10,S03aH02,S04aH02,S01aH08,S02aH08,S03aH01,S01aH01,S04aH01,S01aH02</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1262,7 +1262,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S02aH09,S04aH09,S01aH02,S02aH02,S04aH10,S04aH02,S03aH09,S01aH10,S03aH02,S03aH01,S01aH01,S04aH01,S02aH01,S02aH10,S01aH08,S02aH08,S04aH08,S01aH09,S03aH08,S03aH10</v>
+        <v>S04aH08,S03aH09,S02aH09,S04aH09,S01aH09,S03aH08,S03aH10,S02aH01,S02aH10,S02aH02,S04aH10,S01aH10,S03aH02,S04aH02,S01aH08,S02aH08,S03aH01,S01aH01,S04aH01,S01aH02</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S03aH04,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S03aH03,S03aH02,S04aH05,S04aH08,S02aH06,S03aH05,S03aH08,S04aH07,S04aH02,S02aH02,S01aH06,S02aH03,S04aH03,S01aH02,S04aH04,S01aH03,S01aH04,S01aH07,S02aH07,S02aH04,S02aH05,S04aH06</v>
+        <v>S02aH06,S03aH05,S03aH08,S04aH07,S03aH04,S01aH04,S01aH07,S02aH07,S02aH04,S02aH05,S04aH03,S03aH03,S04aH02,S03aH02,S01aH02,S04aH04,S02aH02,S01aH03,S01aH06,S02aH03,S04aH06,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S04aH05,S04aH08</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1390,7 +1390,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87774CA2-18C3-488E-BC4F-99A0479CCE3A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7FF6A68-161B-4923-AF91-72638492BCF9}">
   <dimension ref="A9:G20"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1524,7 +1524,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDE40561-5986-423A-9EFF-9F999DF099C5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CCA9B5C-FF7C-4E3E-963C-F85988A889DF}">
   <dimension ref="B9:O810"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -27186,7 +27186,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CCA883F-9647-413F-89A9-6D3A6ADF5DE9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5F1282A-17A0-4164-AD99-D63C26CF2517}">
   <dimension ref="B9:FT60"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -41639,7 +41639,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E344CD3B-12D2-4F9F-AF2E-B4DFD3BDAE1B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5926DDE-A9E5-42A2-B456-87FF98AF78D1}">
   <dimension ref="A9:S126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -41784,7 +41784,7 @@
         <v>41</v>
       </c>
       <c r="R12">
-        <v>0.17526666666666665</v>
+        <v>0.17526666666666668</v>
       </c>
       <c r="S12" t="s">
         <v>221</v>
@@ -42071,7 +42071,7 @@
         <v>37</v>
       </c>
       <c r="R19">
-        <v>0.23840000000000003</v>
+        <v>0.23839999999999997</v>
       </c>
       <c r="S19" t="s">
         <v>221</v>
@@ -42112,7 +42112,7 @@
         <v>41</v>
       </c>
       <c r="R20">
-        <v>0.23150000000000001</v>
+        <v>0.23149999999999996</v>
       </c>
       <c r="S20" t="s">
         <v>221</v>
@@ -42768,7 +42768,7 @@
         <v>41</v>
       </c>
       <c r="R36">
-        <v>0.32773333333333338</v>
+        <v>0.32773333333333332</v>
       </c>
       <c r="S36" t="s">
         <v>221</v>
@@ -43096,7 +43096,7 @@
         <v>41</v>
       </c>
       <c r="R44">
-        <v>0.34233333333333338</v>
+        <v>0.34233333333333332</v>
       </c>
       <c r="S44" t="s">
         <v>221</v>
@@ -43219,7 +43219,7 @@
         <v>37</v>
       </c>
       <c r="R47">
-        <v>0.30260000000000004</v>
+        <v>0.30259999999999998</v>
       </c>
       <c r="S47" t="s">
         <v>221</v>
@@ -43362,7 +43362,7 @@
         <v>37</v>
       </c>
       <c r="R51">
-        <v>0.31676666666666664</v>
+        <v>0.3167666666666667</v>
       </c>
       <c r="S51" t="s">
         <v>221</v>
@@ -43382,7 +43382,7 @@
         <v>41</v>
       </c>
       <c r="R52">
-        <v>0.32276666666666665</v>
+        <v>0.3227666666666667</v>
       </c>
       <c r="S52" t="s">
         <v>221</v>
@@ -43462,7 +43462,7 @@
         <v>41</v>
       </c>
       <c r="R56">
-        <v>0.35000000000000003</v>
+        <v>0.34999999999999992</v>
       </c>
       <c r="S56" t="s">
         <v>221</v>
@@ -43522,7 +43522,7 @@
         <v>37</v>
       </c>
       <c r="R59">
-        <v>0.29859999999999998</v>
+        <v>0.29860000000000003</v>
       </c>
       <c r="S59" t="s">
         <v>221</v>
@@ -43682,7 +43682,7 @@
         <v>37</v>
       </c>
       <c r="R67">
-        <v>0.37279999999999996</v>
+        <v>0.37280000000000002</v>
       </c>
       <c r="S67" t="s">
         <v>221</v>
@@ -43702,7 +43702,7 @@
         <v>41</v>
       </c>
       <c r="R68">
-        <v>0.38203333333333328</v>
+        <v>0.38203333333333339</v>
       </c>
       <c r="S68" t="s">
         <v>221</v>
@@ -44022,7 +44022,7 @@
         <v>41</v>
       </c>
       <c r="R84">
-        <v>0.3323666666666667</v>
+        <v>0.33236666666666664</v>
       </c>
       <c r="S84" t="s">
         <v>221</v>
@@ -44170,7 +44170,7 @@
         <v>41</v>
       </c>
       <c r="R92">
-        <v>0.31546666666666667</v>
+        <v>0.31546666666666673</v>
       </c>
       <c r="S92" t="s">
         <v>221</v>
@@ -44324,7 +44324,7 @@
         <v>37</v>
       </c>
       <c r="R103">
-        <v>0.28610000000000002</v>
+        <v>0.28609999999999997</v>
       </c>
       <c r="S103" t="s">
         <v>221</v>
@@ -44338,7 +44338,7 @@
         <v>41</v>
       </c>
       <c r="R104">
-        <v>0.32653333333333329</v>
+        <v>0.32653333333333334</v>
       </c>
       <c r="S104" t="s">
         <v>221</v>
@@ -44380,7 +44380,7 @@
         <v>37</v>
       </c>
       <c r="R107">
-        <v>0.32646666666666663</v>
+        <v>0.32646666666666668</v>
       </c>
       <c r="S107" t="s">
         <v>221</v>
@@ -44394,7 +44394,7 @@
         <v>41</v>
       </c>
       <c r="R108">
-        <v>0.32569999999999999</v>
+        <v>0.32569999999999993</v>
       </c>
       <c r="S108" t="s">
         <v>221</v>
@@ -44506,7 +44506,7 @@
         <v>41</v>
       </c>
       <c r="R116">
-        <v>0.32293333333333335</v>
+        <v>0.32293333333333329</v>
       </c>
       <c r="S116" t="s">
         <v>221</v>
@@ -44548,7 +44548,7 @@
         <v>37</v>
       </c>
       <c r="R119">
-        <v>0.31936666666666669</v>
+        <v>0.31936666666666663</v>
       </c>
       <c r="S119" t="s">
         <v>221</v>
@@ -44604,7 +44604,7 @@
         <v>37</v>
       </c>
       <c r="R123">
-        <v>0.30760000000000004</v>
+        <v>0.30759999999999998</v>
       </c>
       <c r="S123" t="s">
         <v>221</v>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/Scen_TSParameters_ts_40.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/Scen_TSParameters_ts_40.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1E9413C-5C0B-46B9-9222-A5C61258B555}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF29FEC3-DB58-4351-8B53-0B45C5986688}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -675,13 +675,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S02aH06,S03aH05,S03aH08,S04aH07,S03aH04,S01aH04,S01aH07,S02aH07,S02aH04,S02aH05,S04aH03,S03aH03,S04aH02,S03aH02,S01aH02,S04aH04,S02aH02,S01aH03,S01aH06,S02aH03,S04aH06,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S04aH05,S04aH08</t>
+    <t>S04aH02,S01aH03,S01aH04,S01aH07,S02aH07,S04aH03,S03aH02,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S02aH04,S02aH05,S03aH03,S02aH02,S01aH06,S02aH03,S04aH05,S04aH08,S02aH06,S03aH05,S03aH08,S04aH07,S04aH06,S03aH04,S01aH02,S04aH04</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S04aH08,S03aH09,S02aH09,S04aH09,S01aH09,S03aH08,S03aH10,S02aH01,S02aH10,S02aH02,S04aH10,S01aH10,S03aH02,S04aH02,S01aH08,S02aH08,S03aH01,S01aH01,S04aH01,S01aH02</t>
+    <t>S01aH10,S03aH02,S01aH09,S02aH01,S02aH10,S04aH02,S01aH02,S03aH08,S03aH10,S02aH02,S04aH10,S03aH01,S01aH01,S04aH01,S03aH09,S02aH09,S04aH09,S04aH08,S01aH08,S02aH08</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1262,7 +1262,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S04aH08,S03aH09,S02aH09,S04aH09,S01aH09,S03aH08,S03aH10,S02aH01,S02aH10,S02aH02,S04aH10,S01aH10,S03aH02,S04aH02,S01aH08,S02aH08,S03aH01,S01aH01,S04aH01,S01aH02</v>
+        <v>S01aH10,S03aH02,S01aH09,S02aH01,S02aH10,S04aH02,S01aH02,S03aH08,S03aH10,S02aH02,S04aH10,S03aH01,S01aH01,S04aH01,S03aH09,S02aH09,S04aH09,S04aH08,S01aH08,S02aH08</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S02aH06,S03aH05,S03aH08,S04aH07,S03aH04,S01aH04,S01aH07,S02aH07,S02aH04,S02aH05,S04aH03,S03aH03,S04aH02,S03aH02,S01aH02,S04aH04,S02aH02,S01aH03,S01aH06,S02aH03,S04aH06,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S04aH05,S04aH08</v>
+        <v>S04aH02,S01aH03,S01aH04,S01aH07,S02aH07,S04aH03,S03aH02,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S02aH04,S02aH05,S03aH03,S02aH02,S01aH06,S02aH03,S04aH05,S04aH08,S02aH06,S03aH05,S03aH08,S04aH07,S04aH06,S03aH04,S01aH02,S04aH04</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1390,7 +1390,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7FF6A68-161B-4923-AF91-72638492BCF9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E23184D5-499F-4A6E-9F0B-BD21D607E5D5}">
   <dimension ref="A9:G20"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1524,7 +1524,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CCA9B5C-FF7C-4E3E-963C-F85988A889DF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F485DC1A-D30B-4A5F-B1FF-B09BB781CBC7}">
   <dimension ref="B9:O810"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -27186,7 +27186,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5F1282A-17A0-4164-AD99-D63C26CF2517}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C445697-B49E-4254-85C4-F2638B2CFC51}">
   <dimension ref="B9:FT60"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -41639,7 +41639,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5926DDE-A9E5-42A2-B456-87FF98AF78D1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBA511F1-DA30-445A-B68D-BC129815A23F}">
   <dimension ref="A9:S126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -41866,7 +41866,7 @@
         <v>45</v>
       </c>
       <c r="R14">
-        <v>0.19109999999999996</v>
+        <v>0.19110000000000002</v>
       </c>
       <c r="S14" t="s">
         <v>221</v>
@@ -41907,7 +41907,7 @@
         <v>37</v>
       </c>
       <c r="R15">
-        <v>0.20653333333333335</v>
+        <v>0.20653333333333332</v>
       </c>
       <c r="S15" t="s">
         <v>221</v>
@@ -42071,7 +42071,7 @@
         <v>37</v>
       </c>
       <c r="R19">
-        <v>0.23839999999999997</v>
+        <v>0.23840000000000003</v>
       </c>
       <c r="S19" t="s">
         <v>221</v>
@@ -42112,7 +42112,7 @@
         <v>41</v>
       </c>
       <c r="R20">
-        <v>0.23149999999999996</v>
+        <v>0.23150000000000001</v>
       </c>
       <c r="S20" t="s">
         <v>221</v>
@@ -42153,7 +42153,7 @@
         <v>43</v>
       </c>
       <c r="R21">
-        <v>0.12036666666666666</v>
+        <v>0.12036666666666668</v>
       </c>
       <c r="S21" t="s">
         <v>221</v>
@@ -42768,7 +42768,7 @@
         <v>41</v>
       </c>
       <c r="R36">
-        <v>0.32773333333333332</v>
+        <v>0.32773333333333338</v>
       </c>
       <c r="S36" t="s">
         <v>221</v>
@@ -42850,7 +42850,7 @@
         <v>45</v>
       </c>
       <c r="R38">
-        <v>0.20659999999999998</v>
+        <v>0.20660000000000001</v>
       </c>
       <c r="S38" t="s">
         <v>221</v>
@@ -43014,7 +43014,7 @@
         <v>45</v>
       </c>
       <c r="R42">
-        <v>0.29533333333333339</v>
+        <v>0.29533333333333334</v>
       </c>
       <c r="S42" t="s">
         <v>221</v>
@@ -43096,7 +43096,7 @@
         <v>41</v>
       </c>
       <c r="R44">
-        <v>0.34233333333333332</v>
+        <v>0.34233333333333338</v>
       </c>
       <c r="S44" t="s">
         <v>221</v>
@@ -43178,7 +43178,7 @@
         <v>45</v>
       </c>
       <c r="R46">
-        <v>0.22879999999999998</v>
+        <v>0.2288</v>
       </c>
       <c r="S46" t="s">
         <v>221</v>
@@ -43362,7 +43362,7 @@
         <v>37</v>
       </c>
       <c r="R51">
-        <v>0.3167666666666667</v>
+        <v>0.31676666666666664</v>
       </c>
       <c r="S51" t="s">
         <v>221</v>
@@ -43462,7 +43462,7 @@
         <v>41</v>
       </c>
       <c r="R56">
-        <v>0.34999999999999992</v>
+        <v>0.35000000000000003</v>
       </c>
       <c r="S56" t="s">
         <v>221</v>
@@ -43562,7 +43562,7 @@
         <v>43</v>
       </c>
       <c r="R61">
-        <v>0.20516666666666664</v>
+        <v>0.20516666666666669</v>
       </c>
       <c r="S61" t="s">
         <v>221</v>
@@ -43622,7 +43622,7 @@
         <v>41</v>
       </c>
       <c r="R64">
-        <v>0.3297666666666666</v>
+        <v>0.32976666666666665</v>
       </c>
       <c r="S64" t="s">
         <v>221</v>
@@ -43662,7 +43662,7 @@
         <v>45</v>
       </c>
       <c r="R66">
-        <v>0.19193333333333332</v>
+        <v>0.19193333333333337</v>
       </c>
       <c r="S66" t="s">
         <v>221</v>
@@ -43702,7 +43702,7 @@
         <v>41</v>
       </c>
       <c r="R68">
-        <v>0.38203333333333339</v>
+        <v>0.38203333333333328</v>
       </c>
       <c r="S68" t="s">
         <v>221</v>
@@ -43742,7 +43742,7 @@
         <v>45</v>
       </c>
       <c r="R70">
-        <v>0.27233333333333337</v>
+        <v>0.27233333333333332</v>
       </c>
       <c r="S70" t="s">
         <v>221</v>
@@ -43802,7 +43802,7 @@
         <v>43</v>
       </c>
       <c r="R73">
-        <v>0.19603333333333331</v>
+        <v>0.19603333333333336</v>
       </c>
       <c r="S73" t="s">
         <v>221</v>
@@ -43882,7 +43882,7 @@
         <v>43</v>
       </c>
       <c r="R77">
-        <v>0.21280000000000002</v>
+        <v>0.21279999999999999</v>
       </c>
       <c r="S77" t="s">
         <v>221</v>
@@ -43922,7 +43922,7 @@
         <v>37</v>
       </c>
       <c r="R79">
-        <v>0.32426666666666665</v>
+        <v>0.3242666666666667</v>
       </c>
       <c r="S79" t="s">
         <v>221</v>
@@ -44002,7 +44002,7 @@
         <v>37</v>
       </c>
       <c r="R83">
-        <v>0.30743333333333328</v>
+        <v>0.30743333333333334</v>
       </c>
       <c r="S83" t="s">
         <v>221</v>
@@ -44022,7 +44022,7 @@
         <v>41</v>
       </c>
       <c r="R84">
-        <v>0.33236666666666664</v>
+        <v>0.3323666666666667</v>
       </c>
       <c r="S84" t="s">
         <v>221</v>
@@ -44156,7 +44156,7 @@
         <v>37</v>
       </c>
       <c r="R91">
-        <v>0.31433333333333335</v>
+        <v>0.3143333333333333</v>
       </c>
       <c r="S91" t="s">
         <v>221</v>
@@ -44324,7 +44324,7 @@
         <v>37</v>
       </c>
       <c r="R103">
-        <v>0.28609999999999997</v>
+        <v>0.28610000000000002</v>
       </c>
       <c r="S103" t="s">
         <v>221</v>
@@ -44338,7 +44338,7 @@
         <v>41</v>
       </c>
       <c r="R104">
-        <v>0.32653333333333334</v>
+        <v>0.32653333333333329</v>
       </c>
       <c r="S104" t="s">
         <v>221</v>
@@ -44352,7 +44352,7 @@
         <v>43</v>
       </c>
       <c r="R105">
-        <v>0.1952666666666667</v>
+        <v>0.19526666666666667</v>
       </c>
       <c r="S105" t="s">
         <v>221</v>
@@ -44366,7 +44366,7 @@
         <v>45</v>
       </c>
       <c r="R106">
-        <v>0.17756666666666665</v>
+        <v>0.17756666666666668</v>
       </c>
       <c r="S106" t="s">
         <v>221</v>
@@ -44380,7 +44380,7 @@
         <v>37</v>
       </c>
       <c r="R107">
-        <v>0.32646666666666668</v>
+        <v>0.32646666666666663</v>
       </c>
       <c r="S107" t="s">
         <v>221</v>
@@ -44436,7 +44436,7 @@
         <v>37</v>
       </c>
       <c r="R111">
-        <v>0.31430000000000002</v>
+        <v>0.31429999999999997</v>
       </c>
       <c r="S111" t="s">
         <v>221</v>
@@ -44506,7 +44506,7 @@
         <v>41</v>
       </c>
       <c r="R116">
-        <v>0.32293333333333329</v>
+        <v>0.32293333333333335</v>
       </c>
       <c r="S116" t="s">
         <v>221</v>
@@ -44590,7 +44590,7 @@
         <v>45</v>
       </c>
       <c r="R122">
-        <v>0.23020000000000004</v>
+        <v>0.23019999999999999</v>
       </c>
       <c r="S122" t="s">
         <v>221</v>
@@ -44604,7 +44604,7 @@
         <v>37</v>
       </c>
       <c r="R123">
-        <v>0.30759999999999998</v>
+        <v>0.30760000000000004</v>
       </c>
       <c r="S123" t="s">
         <v>221</v>
@@ -44618,7 +44618,7 @@
         <v>41</v>
       </c>
       <c r="R124">
-        <v>0.3557333333333334</v>
+        <v>0.35573333333333329</v>
       </c>
       <c r="S124" t="s">
         <v>221</v>
@@ -44632,7 +44632,7 @@
         <v>43</v>
       </c>
       <c r="R125">
-        <v>0.17353333333333332</v>
+        <v>0.17353333333333334</v>
       </c>
       <c r="S125" t="s">
         <v>221</v>
@@ -44646,7 +44646,7 @@
         <v>45</v>
       </c>
       <c r="R126">
-        <v>0.21530000000000002</v>
+        <v>0.21529999999999996</v>
       </c>
       <c r="S126" t="s">
         <v>221</v>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/Scen_TSParameters_ts_40.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/Scen_TSParameters_ts_40.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C185695D-5549-4B80-9223-9EF7B28175A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4957C919-5B6D-4A58-9566-100D12CD7FBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -699,13 +699,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S04aH03,S01aH02,S04aH04,S03aH04,S03aH03,S04aH05,S04aH08,S02aH06,S03aH05,S03aH08,S04aH07,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S02aH02,S03aH02,S01aH03,S04aH06,S01aH04,S01aH07,S02aH07,S01aH06,S02aH03,S02aH04,S02aH05,S04aH02</t>
+    <t>S02aH04,S02aH05,S02aH02,S01aH02,S04aH04,S01aH03,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S01aH06,S02aH03,S04aH05,S04aH08,S04aH02,S04aH03,S02aH06,S03aH05,S03aH08,S04aH07,S01aH04,S01aH07,S02aH07,S03aH03,S04aH06,S03aH04,S03aH02</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S02aH01,S02aH10,S01aH08,S02aH08,S02aH09,S04aH09,S02aH02,S04aH10,S04aH08,S03aH09,S01aH02,S03aH01,S04aH02,S01aH09,S01aH01,S04aH01,S03aH08,S03aH10,S01aH10,S03aH02</t>
+    <t>S03aH08,S03aH10,S03aH01,S01aH08,S02aH08,S01aH02,S01aH01,S04aH01,S01aH10,S03aH02,S02aH01,S02aH10,S04aH08,S03aH09,S01aH09,S02aH02,S04aH10,S02aH09,S04aH09,S04aH02</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1291,7 +1291,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S02aH01,S02aH10,S01aH08,S02aH08,S02aH09,S04aH09,S02aH02,S04aH10,S04aH08,S03aH09,S01aH02,S03aH01,S04aH02,S01aH09,S01aH01,S04aH01,S03aH08,S03aH10,S01aH10,S03aH02</v>
+        <v>S03aH08,S03aH10,S03aH01,S01aH08,S02aH08,S01aH02,S01aH01,S04aH01,S01aH10,S03aH02,S02aH01,S02aH10,S04aH08,S03aH09,S01aH09,S02aH02,S04aH10,S02aH09,S04aH09,S04aH02</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S04aH03,S01aH02,S04aH04,S03aH04,S03aH03,S04aH05,S04aH08,S02aH06,S03aH05,S03aH08,S04aH07,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S02aH02,S03aH02,S01aH03,S04aH06,S01aH04,S01aH07,S02aH07,S01aH06,S02aH03,S02aH04,S02aH05,S04aH02</v>
+        <v>S02aH04,S02aH05,S02aH02,S01aH02,S04aH04,S01aH03,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S01aH06,S02aH03,S04aH05,S04aH08,S04aH02,S04aH03,S02aH06,S03aH05,S03aH08,S04aH07,S01aH04,S01aH07,S02aH07,S03aH03,S04aH06,S03aH04,S03aH02</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1430,7 +1430,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE8A5799-6053-42BC-944F-8521AF53A222}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B0561A1-3202-4979-9FAE-8E32306AD90A}">
   <dimension ref="A9:G20"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1564,7 +1564,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A3640E7-AED7-4E4D-9551-33D22EDFDFFE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAB9C6CB-87A8-4827-978F-3DC73ADC8E36}">
   <dimension ref="B9:O810"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -27226,7 +27226,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B779014F-D742-4F53-A934-44BA1AD63C2A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4AEF7D72-860B-40A9-8FF1-05E786045ADD}">
   <dimension ref="B9:HS60"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -59999,7 +59999,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CC76845-53A6-4A78-93F9-72154DFEE231}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FAD6BAB-35E9-4CFE-A59B-D638B48FEBD7}">
   <dimension ref="A9:S126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -60226,7 +60226,7 @@
         <v>46</v>
       </c>
       <c r="R14">
-        <v>0.19110000000000002</v>
+        <v>0.19109999999999996</v>
       </c>
       <c r="S14" t="s">
         <v>229</v>
@@ -60267,7 +60267,7 @@
         <v>38</v>
       </c>
       <c r="R15">
-        <v>0.20653333333333335</v>
+        <v>0.20653333333333332</v>
       </c>
       <c r="S15" t="s">
         <v>229</v>
@@ -60513,7 +60513,7 @@
         <v>44</v>
       </c>
       <c r="R21">
-        <v>0.12036666666666668</v>
+        <v>0.12036666666666666</v>
       </c>
       <c r="S21" t="s">
         <v>229</v>
@@ -61210,7 +61210,7 @@
         <v>46</v>
       </c>
       <c r="R38">
-        <v>0.20660000000000001</v>
+        <v>0.20659999999999998</v>
       </c>
       <c r="S38" t="s">
         <v>229</v>
@@ -61374,7 +61374,7 @@
         <v>46</v>
       </c>
       <c r="R42">
-        <v>0.29533333333333334</v>
+        <v>0.29533333333333339</v>
       </c>
       <c r="S42" t="s">
         <v>229</v>
@@ -61538,7 +61538,7 @@
         <v>46</v>
       </c>
       <c r="R46">
-        <v>0.2288</v>
+        <v>0.22879999999999998</v>
       </c>
       <c r="S46" t="s">
         <v>229</v>
@@ -61579,7 +61579,7 @@
         <v>38</v>
       </c>
       <c r="R47">
-        <v>0.30260000000000004</v>
+        <v>0.30259999999999998</v>
       </c>
       <c r="S47" t="s">
         <v>229</v>
@@ -61882,7 +61882,7 @@
         <v>38</v>
       </c>
       <c r="R59">
-        <v>0.29859999999999998</v>
+        <v>0.29860000000000003</v>
       </c>
       <c r="S59" t="s">
         <v>229</v>
@@ -61922,7 +61922,7 @@
         <v>44</v>
       </c>
       <c r="R61">
-        <v>0.20516666666666669</v>
+        <v>0.20516666666666664</v>
       </c>
       <c r="S61" t="s">
         <v>229</v>
@@ -62022,7 +62022,7 @@
         <v>46</v>
       </c>
       <c r="R66">
-        <v>0.19193333333333337</v>
+        <v>0.19193333333333332</v>
       </c>
       <c r="S66" t="s">
         <v>229</v>
@@ -62042,7 +62042,7 @@
         <v>38</v>
       </c>
       <c r="R67">
-        <v>0.37279999999999996</v>
+        <v>0.37280000000000002</v>
       </c>
       <c r="S67" t="s">
         <v>229</v>
@@ -62102,7 +62102,7 @@
         <v>46</v>
       </c>
       <c r="R70">
-        <v>0.27233333333333332</v>
+        <v>0.27233333333333337</v>
       </c>
       <c r="S70" t="s">
         <v>229</v>
@@ -62162,7 +62162,7 @@
         <v>44</v>
       </c>
       <c r="R73">
-        <v>0.19603333333333336</v>
+        <v>0.19603333333333331</v>
       </c>
       <c r="S73" t="s">
         <v>229</v>
@@ -62242,7 +62242,7 @@
         <v>44</v>
       </c>
       <c r="R77">
-        <v>0.21279999999999999</v>
+        <v>0.21280000000000002</v>
       </c>
       <c r="S77" t="s">
         <v>229</v>
@@ -62282,7 +62282,7 @@
         <v>38</v>
       </c>
       <c r="R79">
-        <v>0.32426666666666665</v>
+        <v>0.3242666666666667</v>
       </c>
       <c r="S79" t="s">
         <v>229</v>
@@ -62362,7 +62362,7 @@
         <v>38</v>
       </c>
       <c r="R83">
-        <v>0.30743333333333328</v>
+        <v>0.30743333333333334</v>
       </c>
       <c r="S83" t="s">
         <v>229</v>
@@ -62516,7 +62516,7 @@
         <v>38</v>
       </c>
       <c r="R91">
-        <v>0.31433333333333335</v>
+        <v>0.3143333333333333</v>
       </c>
       <c r="S91" t="s">
         <v>229</v>
@@ -62712,7 +62712,7 @@
         <v>44</v>
       </c>
       <c r="R105">
-        <v>0.19526666666666667</v>
+        <v>0.1952666666666667</v>
       </c>
       <c r="S105" t="s">
         <v>229</v>
@@ -62726,7 +62726,7 @@
         <v>46</v>
       </c>
       <c r="R106">
-        <v>0.17756666666666668</v>
+        <v>0.17756666666666665</v>
       </c>
       <c r="S106" t="s">
         <v>229</v>
@@ -62796,7 +62796,7 @@
         <v>38</v>
       </c>
       <c r="R111">
-        <v>0.31430000000000002</v>
+        <v>0.31429999999999997</v>
       </c>
       <c r="S111" t="s">
         <v>229</v>
@@ -62908,7 +62908,7 @@
         <v>38</v>
       </c>
       <c r="R119">
-        <v>0.31936666666666669</v>
+        <v>0.31936666666666663</v>
       </c>
       <c r="S119" t="s">
         <v>229</v>
@@ -62950,7 +62950,7 @@
         <v>46</v>
       </c>
       <c r="R122">
-        <v>0.23019999999999999</v>
+        <v>0.23020000000000004</v>
       </c>
       <c r="S122" t="s">
         <v>229</v>
@@ -62992,7 +62992,7 @@
         <v>44</v>
       </c>
       <c r="R125">
-        <v>0.17353333333333334</v>
+        <v>0.17353333333333332</v>
       </c>
       <c r="S125" t="s">
         <v>229</v>
@@ -63006,7 +63006,7 @@
         <v>46</v>
       </c>
       <c r="R126">
-        <v>0.21529999999999996</v>
+        <v>0.21530000000000002</v>
       </c>
       <c r="S126" t="s">
         <v>229</v>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/Scen_TSParameters_ts_40.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/Scen_TSParameters_ts_40.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4957C919-5B6D-4A58-9566-100D12CD7FBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1A28DC8-BB33-405C-B5DF-1487CFED3DBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -699,13 +699,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S02aH04,S02aH05,S02aH02,S01aH02,S04aH04,S01aH03,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S01aH06,S02aH03,S04aH05,S04aH08,S04aH02,S04aH03,S02aH06,S03aH05,S03aH08,S04aH07,S01aH04,S01aH07,S02aH07,S03aH03,S04aH06,S03aH04,S03aH02</t>
+    <t>S03aH04,S01aH06,S02aH03,S03aH02,S04aH06,S02aH02,S03aH03,S04aH03,S04aH02,S01aH02,S04aH04,S02aH04,S02aH05,S04aH05,S04aH08,S01aH04,S01aH07,S02aH07,S01aH03,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S02aH06,S03aH05,S03aH08,S04aH07</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S03aH08,S03aH10,S03aH01,S01aH08,S02aH08,S01aH02,S01aH01,S04aH01,S01aH10,S03aH02,S02aH01,S02aH10,S04aH08,S03aH09,S01aH09,S02aH02,S04aH10,S02aH09,S04aH09,S04aH02</t>
+    <t>S02aH09,S04aH09,S01aH01,S04aH01,S04aH02,S03aH01,S02aH02,S04aH10,S02aH01,S02aH10,S01aH10,S03aH02,S01aH08,S02aH08,S03aH08,S03aH10,S01aH09,S01aH02,S04aH08,S03aH09</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1291,7 +1291,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S03aH08,S03aH10,S03aH01,S01aH08,S02aH08,S01aH02,S01aH01,S04aH01,S01aH10,S03aH02,S02aH01,S02aH10,S04aH08,S03aH09,S01aH09,S02aH02,S04aH10,S02aH09,S04aH09,S04aH02</v>
+        <v>S02aH09,S04aH09,S01aH01,S04aH01,S04aH02,S03aH01,S02aH02,S04aH10,S02aH01,S02aH10,S01aH10,S03aH02,S01aH08,S02aH08,S03aH08,S03aH10,S01aH09,S01aH02,S04aH08,S03aH09</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S02aH04,S02aH05,S02aH02,S01aH02,S04aH04,S01aH03,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S01aH06,S02aH03,S04aH05,S04aH08,S04aH02,S04aH03,S02aH06,S03aH05,S03aH08,S04aH07,S01aH04,S01aH07,S02aH07,S03aH03,S04aH06,S03aH04,S03aH02</v>
+        <v>S03aH04,S01aH06,S02aH03,S03aH02,S04aH06,S02aH02,S03aH03,S04aH03,S04aH02,S01aH02,S04aH04,S02aH04,S02aH05,S04aH05,S04aH08,S01aH04,S01aH07,S02aH07,S01aH03,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S02aH06,S03aH05,S03aH08,S04aH07</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1430,7 +1430,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B0561A1-3202-4979-9FAE-8E32306AD90A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54507A26-ED65-4B4D-8A30-CB50ADD6F659}">
   <dimension ref="A9:G20"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1564,7 +1564,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAB9C6CB-87A8-4827-978F-3DC73ADC8E36}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CDC6CDB-7C6D-4433-A5F0-654440CFBEDD}">
   <dimension ref="B9:O810"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -27226,7 +27226,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4AEF7D72-860B-40A9-8FF1-05E786045ADD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FAF03C0-B9A4-4A5C-9AAD-3F48C48DCE17}">
   <dimension ref="B9:HS60"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -59999,7 +59999,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FAD6BAB-35E9-4CFE-A59B-D638B48FEBD7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59184168-F93C-4F54-8165-370EED9AADCA}">
   <dimension ref="A9:S126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -60267,7 +60267,7 @@
         <v>38</v>
       </c>
       <c r="R15">
-        <v>0.20653333333333332</v>
+        <v>0.20653333333333335</v>
       </c>
       <c r="S15" t="s">
         <v>229</v>
@@ -61579,7 +61579,7 @@
         <v>38</v>
       </c>
       <c r="R47">
-        <v>0.30259999999999998</v>
+        <v>0.30260000000000004</v>
       </c>
       <c r="S47" t="s">
         <v>229</v>
@@ -61882,7 +61882,7 @@
         <v>38</v>
       </c>
       <c r="R59">
-        <v>0.29860000000000003</v>
+        <v>0.29859999999999998</v>
       </c>
       <c r="S59" t="s">
         <v>229</v>
@@ -62042,7 +62042,7 @@
         <v>38</v>
       </c>
       <c r="R67">
-        <v>0.37280000000000002</v>
+        <v>0.37279999999999996</v>
       </c>
       <c r="S67" t="s">
         <v>229</v>
@@ -62282,7 +62282,7 @@
         <v>38</v>
       </c>
       <c r="R79">
-        <v>0.3242666666666667</v>
+        <v>0.32426666666666665</v>
       </c>
       <c r="S79" t="s">
         <v>229</v>
@@ -62362,7 +62362,7 @@
         <v>38</v>
       </c>
       <c r="R83">
-        <v>0.30743333333333334</v>
+        <v>0.30743333333333328</v>
       </c>
       <c r="S83" t="s">
         <v>229</v>
@@ -62516,7 +62516,7 @@
         <v>38</v>
       </c>
       <c r="R91">
-        <v>0.3143333333333333</v>
+        <v>0.31433333333333335</v>
       </c>
       <c r="S91" t="s">
         <v>229</v>
@@ -62796,7 +62796,7 @@
         <v>38</v>
       </c>
       <c r="R111">
-        <v>0.31429999999999997</v>
+        <v>0.31430000000000002</v>
       </c>
       <c r="S111" t="s">
         <v>229</v>
@@ -62908,7 +62908,7 @@
         <v>38</v>
       </c>
       <c r="R119">
-        <v>0.31936666666666663</v>
+        <v>0.31936666666666669</v>
       </c>
       <c r="S119" t="s">
         <v>229</v>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/Scen_TSParameters_ts_40.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/Scen_TSParameters_ts_40.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61DE3951-608B-4CBD-9A2B-2C4B7E9A755B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52A40D58-9129-411C-8FFA-6EF5580ADD60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -699,13 +699,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S04aH03,S02aH06,S03aH05,S03aH08,S04aH07,S02aH04,S02aH05,S02aH02,S01aH02,S04aH04,S04aH02,S01aH06,S02aH03,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S03aH02,S04aH06,S01aH04,S01aH07,S02aH07,S01aH03,S04aH05,S04aH08,S03aH03,S03aH04</t>
+    <t>S01aH06,S02aH03,S04aH05,S04aH08,S03aH04,S03aH02,S03aH03,S02aH02,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S04aH06,S01aH02,S04aH04,S04aH02,S01aH04,S01aH07,S02aH07,S04aH03,S02aH06,S03aH05,S03aH08,S04aH07,S02aH04,S02aH05,S01aH03</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S02aH01,S02aH10,S03aH09,S03aH08,S03aH10,S04aH08,S03aH01,S01aH08,S02aH08,S01aH10,S03aH02,S01aH01,S04aH01,S01aH02,S04aH02,S01aH09,S02aH02,S04aH10,S02aH09,S04aH09</t>
+    <t>S01aH01,S04aH01,S02aH09,S04aH09,S04aH02,S02aH02,S04aH10,S03aH01,S01aH02,S01aH08,S02aH08,S01aH10,S03aH02,S01aH09,S02aH01,S02aH10,S04aH08,S03aH09,S03aH08,S03aH10</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1291,7 +1291,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S02aH01,S02aH10,S03aH09,S03aH08,S03aH10,S04aH08,S03aH01,S01aH08,S02aH08,S01aH10,S03aH02,S01aH01,S04aH01,S01aH02,S04aH02,S01aH09,S02aH02,S04aH10,S02aH09,S04aH09</v>
+        <v>S01aH01,S04aH01,S02aH09,S04aH09,S04aH02,S02aH02,S04aH10,S03aH01,S01aH02,S01aH08,S02aH08,S01aH10,S03aH02,S01aH09,S02aH01,S02aH10,S04aH08,S03aH09,S03aH08,S03aH10</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S04aH03,S02aH06,S03aH05,S03aH08,S04aH07,S02aH04,S02aH05,S02aH02,S01aH02,S04aH04,S04aH02,S01aH06,S02aH03,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S03aH02,S04aH06,S01aH04,S01aH07,S02aH07,S01aH03,S04aH05,S04aH08,S03aH03,S03aH04</v>
+        <v>S01aH06,S02aH03,S04aH05,S04aH08,S03aH04,S03aH02,S03aH03,S02aH02,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S04aH06,S01aH02,S04aH04,S04aH02,S01aH04,S01aH07,S02aH07,S04aH03,S02aH06,S03aH05,S03aH08,S04aH07,S02aH04,S02aH05,S01aH03</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1430,7 +1430,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B50A8859-6F60-4A44-A726-0EC79D4CDA11}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E711720-3275-459F-9CF6-940F50AB4C93}">
   <dimension ref="A9:G20"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1564,7 +1564,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F84FBDBA-34DD-4EBF-B33C-F40945806182}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{940EBD20-C268-47EB-AF36-2C737D5AD5CD}">
   <dimension ref="B9:O810"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -27226,7 +27226,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53EB7AE7-0BB6-430C-B148-9678D692BDBF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED78233E-CCED-4521-90E6-6597778DD0D6}">
   <dimension ref="B9:HS60"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -59999,7 +59999,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3BD10B9-9381-4545-B174-52911A8F18B7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCCDFD1E-3F3B-428C-A1DF-C1288A8FE704}">
   <dimension ref="A9:S126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -60144,7 +60144,7 @@
         <v>42</v>
       </c>
       <c r="R12">
-        <v>0.17526666666666668</v>
+        <v>0.17526666666666665</v>
       </c>
       <c r="S12" t="s">
         <v>229</v>
@@ -60431,7 +60431,7 @@
         <v>38</v>
       </c>
       <c r="R19">
-        <v>0.23839999999999997</v>
+        <v>0.23840000000000003</v>
       </c>
       <c r="S19" t="s">
         <v>229</v>
@@ -60513,7 +60513,7 @@
         <v>44</v>
       </c>
       <c r="R21">
-        <v>0.12036666666666668</v>
+        <v>0.12036666666666666</v>
       </c>
       <c r="S21" t="s">
         <v>229</v>
@@ -61210,7 +61210,7 @@
         <v>46</v>
       </c>
       <c r="R38">
-        <v>0.20660000000000001</v>
+        <v>0.20659999999999998</v>
       </c>
       <c r="S38" t="s">
         <v>229</v>
@@ -61374,7 +61374,7 @@
         <v>46</v>
       </c>
       <c r="R42">
-        <v>0.29533333333333334</v>
+        <v>0.29533333333333339</v>
       </c>
       <c r="S42" t="s">
         <v>229</v>
@@ -61538,7 +61538,7 @@
         <v>46</v>
       </c>
       <c r="R46">
-        <v>0.2288</v>
+        <v>0.22879999999999998</v>
       </c>
       <c r="S46" t="s">
         <v>229</v>
@@ -61579,7 +61579,7 @@
         <v>38</v>
       </c>
       <c r="R47">
-        <v>0.30259999999999998</v>
+        <v>0.30260000000000004</v>
       </c>
       <c r="S47" t="s">
         <v>229</v>
@@ -61702,7 +61702,7 @@
         <v>46</v>
       </c>
       <c r="R50">
-        <v>0.24780000000000002</v>
+        <v>0.24779999999999999</v>
       </c>
       <c r="S50" t="s">
         <v>229</v>
@@ -61722,7 +61722,7 @@
         <v>38</v>
       </c>
       <c r="R51">
-        <v>0.3167666666666667</v>
+        <v>0.31676666666666664</v>
       </c>
       <c r="S51" t="s">
         <v>229</v>
@@ -61742,7 +61742,7 @@
         <v>42</v>
       </c>
       <c r="R52">
-        <v>0.3227666666666667</v>
+        <v>0.32276666666666665</v>
       </c>
       <c r="S52" t="s">
         <v>229</v>
@@ -61782,7 +61782,7 @@
         <v>46</v>
       </c>
       <c r="R54">
-        <v>0.22766666666666666</v>
+        <v>0.22766666666666668</v>
       </c>
       <c r="S54" t="s">
         <v>229</v>
@@ -61882,7 +61882,7 @@
         <v>38</v>
       </c>
       <c r="R59">
-        <v>0.29860000000000003</v>
+        <v>0.29859999999999998</v>
       </c>
       <c r="S59" t="s">
         <v>229</v>
@@ -61922,7 +61922,7 @@
         <v>44</v>
       </c>
       <c r="R61">
-        <v>0.20516666666666669</v>
+        <v>0.20516666666666664</v>
       </c>
       <c r="S61" t="s">
         <v>229</v>
@@ -61982,7 +61982,7 @@
         <v>42</v>
       </c>
       <c r="R64">
-        <v>0.32976666666666665</v>
+        <v>0.3297666666666666</v>
       </c>
       <c r="S64" t="s">
         <v>229</v>
@@ -62022,7 +62022,7 @@
         <v>46</v>
       </c>
       <c r="R66">
-        <v>0.19193333333333337</v>
+        <v>0.19193333333333332</v>
       </c>
       <c r="S66" t="s">
         <v>229</v>
@@ -62042,7 +62042,7 @@
         <v>38</v>
       </c>
       <c r="R67">
-        <v>0.37280000000000002</v>
+        <v>0.37279999999999996</v>
       </c>
       <c r="S67" t="s">
         <v>229</v>
@@ -62102,7 +62102,7 @@
         <v>46</v>
       </c>
       <c r="R70">
-        <v>0.27233333333333332</v>
+        <v>0.27233333333333337</v>
       </c>
       <c r="S70" t="s">
         <v>229</v>
@@ -62162,7 +62162,7 @@
         <v>44</v>
       </c>
       <c r="R73">
-        <v>0.19603333333333336</v>
+        <v>0.19603333333333331</v>
       </c>
       <c r="S73" t="s">
         <v>229</v>
@@ -62242,7 +62242,7 @@
         <v>44</v>
       </c>
       <c r="R77">
-        <v>0.21279999999999999</v>
+        <v>0.21280000000000002</v>
       </c>
       <c r="S77" t="s">
         <v>229</v>
@@ -62530,7 +62530,7 @@
         <v>42</v>
       </c>
       <c r="R92">
-        <v>0.31546666666666673</v>
+        <v>0.31546666666666667</v>
       </c>
       <c r="S92" t="s">
         <v>229</v>
@@ -62558,7 +62558,7 @@
         <v>46</v>
       </c>
       <c r="R94">
-        <v>0.21930000000000002</v>
+        <v>0.21929999999999997</v>
       </c>
       <c r="S94" t="s">
         <v>229</v>
@@ -62684,7 +62684,7 @@
         <v>38</v>
       </c>
       <c r="R103">
-        <v>0.28609999999999997</v>
+        <v>0.28610000000000002</v>
       </c>
       <c r="S103" t="s">
         <v>229</v>
@@ -62712,7 +62712,7 @@
         <v>44</v>
       </c>
       <c r="R105">
-        <v>0.19526666666666667</v>
+        <v>0.1952666666666667</v>
       </c>
       <c r="S105" t="s">
         <v>229</v>
@@ -62726,7 +62726,7 @@
         <v>46</v>
       </c>
       <c r="R106">
-        <v>0.17756666666666668</v>
+        <v>0.17756666666666665</v>
       </c>
       <c r="S106" t="s">
         <v>229</v>
@@ -62740,7 +62740,7 @@
         <v>38</v>
       </c>
       <c r="R107">
-        <v>0.32646666666666668</v>
+        <v>0.32646666666666663</v>
       </c>
       <c r="S107" t="s">
         <v>229</v>
@@ -62754,7 +62754,7 @@
         <v>42</v>
       </c>
       <c r="R108">
-        <v>0.32569999999999993</v>
+        <v>0.32569999999999999</v>
       </c>
       <c r="S108" t="s">
         <v>229</v>
@@ -62908,7 +62908,7 @@
         <v>38</v>
       </c>
       <c r="R119">
-        <v>0.31936666666666663</v>
+        <v>0.31936666666666669</v>
       </c>
       <c r="S119" t="s">
         <v>229</v>
@@ -62964,7 +62964,7 @@
         <v>38</v>
       </c>
       <c r="R123">
-        <v>0.30759999999999998</v>
+        <v>0.30760000000000004</v>
       </c>
       <c r="S123" t="s">
         <v>229</v>
@@ -62978,7 +62978,7 @@
         <v>42</v>
       </c>
       <c r="R124">
-        <v>0.35573333333333329</v>
+        <v>0.3557333333333334</v>
       </c>
       <c r="S124" t="s">
         <v>229</v>
@@ -62992,7 +62992,7 @@
         <v>44</v>
       </c>
       <c r="R125">
-        <v>0.17353333333333334</v>
+        <v>0.17353333333333332</v>
       </c>
       <c r="S125" t="s">
         <v>229</v>
@@ -63006,7 +63006,7 @@
         <v>46</v>
       </c>
       <c r="R126">
-        <v>0.21529999999999996</v>
+        <v>0.21530000000000002</v>
       </c>
       <c r="S126" t="s">
         <v>229</v>
